--- a/scraper/downloads/projects_page_5.xlsx
+++ b/scraper/downloads/projects_page_5.xlsx
@@ -201,11 +201,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
-    <col min="1" max="1" width="22.950000000000003" customWidth="1"/>
+    <col min="1" max="1" width="8.100000000000001" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="10.8" customWidth="1"/>
     <col min="4" max="4" width="9.450000000000001" customWidth="1"/>
-    <col min="5" max="5" width="28.35" customWidth="1"/>
+    <col min="5" max="5" width="54" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
     <col min="7" max="7" width="12.15" customWidth="1"/>
     <col min="8" max="8" width="10.8" customWidth="1"/>
@@ -335,16 +335,14 @@
     <row r="3">
       <c t="inlineStr" r="A3">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B3">
-        <is>
-          <t xml:space="preserve">27-1</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B3" s="65">
+        <v>15</v>
       </c>
       <c r="C3" s="65">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c t="inlineStr" r="D3">
         <is>
@@ -353,64 +351,49 @@
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t xml:space="preserve">b1 apt 5</t>
+          <t xml:space="preserve">mecher 2023-דירה 29 טיפוס G1</t>
         </is>
       </c>
       <c r="F3" s="65">
         <v>3</v>
       </c>
       <c r="G3" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="65">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="I3" s="65">
-        <v>8</v>
-      </c>
-      <c r="N3" s="63">
-        <v>4351320</v>
-      </c>
-      <c r="O3" s="63">
-        <v>4351320</v>
-      </c>
-      <c r="P3" s="63">
-        <v>4650000</v>
-      </c>
-      <c t="inlineStr" r="Q3">
-        <is>
-          <t xml:space="preserve">הרשמה: תמימה זיסקינד</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="L3">
+        <is>
+          <t xml:space="preserve">דרום </t>
+        </is>
+      </c>
+      <c r="N3" s="65">
+        <v>0</v>
+      </c>
+      <c r="O3" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R3">
         <is>
-          <t xml:space="preserve">הרשמה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="S3">
-        <is>
-          <t xml:space="preserve">מנחם אוריאל</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="T3">
-        <is>
-          <t xml:space="preserve">03/09/2025</t>
+          <t xml:space="preserve">פעיל</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B4">
-        <is>
-          <t xml:space="preserve">27-1</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B4" s="65">
+        <v>15</v>
       </c>
       <c r="C4" s="65">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c t="inlineStr" r="D4">
         <is>
@@ -419,26 +402,31 @@
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">b1 apt 6</t>
+          <t xml:space="preserve">mecher 2023-דירה 30 טיפוס H1</t>
         </is>
       </c>
       <c r="F4" s="65">
-        <v>4</v>
-      </c>
-      <c r="G4" s="65">
         <v>3</v>
       </c>
+      <c t="n" r="G4">
+        <v>3.5</v>
+      </c>
       <c r="H4" s="65">
-        <v>64</v>
-      </c>
-      <c r="I4" s="65">
-        <v>7</v>
+        <v>94</v>
+      </c>
+      <c t="n" r="I4">
+        <v>3.4</v>
+      </c>
+      <c t="inlineStr" r="L4">
+        <is>
+          <t xml:space="preserve">דרום מערב </t>
+        </is>
       </c>
       <c r="N4" s="63">
-        <v>3863700</v>
+        <v>5340000</v>
       </c>
       <c r="O4" s="63">
-        <v>3863700</v>
+        <v>5340000</v>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -449,44 +437,47 @@
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B5">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B5" s="65">
+        <v>15</v>
       </c>
       <c r="C5" s="65">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c t="inlineStr" r="D5">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c t="inlineStr" r="E5">
         <is>
-          <t xml:space="preserve">b2 apt 1</t>
+          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
         </is>
       </c>
       <c r="F5" s="65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="65">
-        <v>61</v>
-      </c>
-      <c r="I5" s="65">
-        <v>55</v>
+        <v>88</v>
+      </c>
+      <c t="n" r="I5">
+        <v>6.4</v>
+      </c>
+      <c t="inlineStr" r="L5">
+        <is>
+          <t xml:space="preserve">צפון מערב </t>
+        </is>
       </c>
       <c r="N5" s="63">
-        <v>4064040</v>
+        <v>5210000</v>
       </c>
       <c r="O5" s="63">
-        <v>4064040</v>
+        <v>5210000</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -497,44 +488,47 @@
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B6">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B6" s="65">
+        <v>15</v>
       </c>
       <c r="C6" s="65">
+        <v>33</v>
+      </c>
+      <c t="inlineStr" r="D6">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E6">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
+        </is>
+      </c>
+      <c r="F6" s="65">
+        <v>4</v>
+      </c>
+      <c r="G6" s="65">
         <v>2</v>
       </c>
-      <c t="inlineStr" r="D6">
-        <is>
-          <t xml:space="preserve">דירת גן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E6">
-        <is>
-          <t xml:space="preserve">b2 apt 2</t>
-        </is>
-      </c>
-      <c r="F6" s="65">
-        <v>1</v>
-      </c>
-      <c r="G6" s="65">
-        <v>3</v>
-      </c>
       <c r="H6" s="65">
-        <v>83</v>
-      </c>
-      <c r="I6" s="65">
-        <v>126</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I6">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L6">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
       </c>
       <c r="N6" s="63">
-        <v>5876640</v>
+        <v>3780000</v>
       </c>
       <c r="O6" s="63">
-        <v>5876640</v>
+        <v>3780000</v>
       </c>
       <c t="inlineStr" r="R6">
         <is>
@@ -545,44 +539,47 @@
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B7">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B7" s="65">
+        <v>15</v>
       </c>
       <c r="C7" s="65">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c t="inlineStr" r="D7">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">b2 apt 3</t>
+          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
         </is>
       </c>
       <c r="F7" s="65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="65">
-        <v>82</v>
-      </c>
-      <c r="I7" s="65">
-        <v>130</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I7">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L7">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
       </c>
       <c r="N7" s="63">
-        <v>6237000</v>
+        <v>3770000</v>
       </c>
       <c r="O7" s="63">
-        <v>6237000</v>
+        <v>3770000</v>
       </c>
       <c t="inlineStr" r="R7">
         <is>
@@ -593,64 +590,83 @@
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B8">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B8" s="65">
+        <v>15</v>
       </c>
       <c r="C8" s="65">
+        <v>35</v>
+      </c>
+      <c t="inlineStr" r="D8">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E8">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
+        </is>
+      </c>
+      <c r="F8" s="65">
         <v>4</v>
       </c>
-      <c t="inlineStr" r="D8">
-        <is>
-          <t xml:space="preserve">דירת גן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E8">
-        <is>
-          <t xml:space="preserve">b2 apt 4</t>
-        </is>
-      </c>
-      <c r="F8" s="65">
-        <v>1</v>
-      </c>
       <c r="G8" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" s="65">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c t="n" r="I8">
-        <v>75.5</v>
+        <v>6.9</v>
+      </c>
+      <c t="inlineStr" r="L8">
+        <is>
+          <t xml:space="preserve">מזרח </t>
+        </is>
       </c>
       <c r="N8" s="63">
-        <v>5167800</v>
+        <v>5650000</v>
       </c>
       <c r="O8" s="63">
-        <v>5167800</v>
+        <v>5650000</v>
+      </c>
+      <c r="P8" s="63">
+        <v>6750000</v>
+      </c>
+      <c t="inlineStr" r="Q8">
+        <is>
+          <t xml:space="preserve">הרשמה: Daniel Bassan</t>
+        </is>
       </c>
       <c t="inlineStr" r="R8">
         <is>
-          <t xml:space="preserve">פעיל</t>
+          <t xml:space="preserve">הרשמה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="S8">
+        <is>
+          <t xml:space="preserve">יניב אשכנזי</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="T8">
+        <is>
+          <t xml:space="preserve">30/03/2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B9">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B9" s="65">
+        <v>15</v>
       </c>
       <c r="C9" s="65">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c t="inlineStr" r="D9">
         <is>
@@ -659,26 +675,31 @@
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">b2 apt 5</t>
+          <t xml:space="preserve">mecher 2023-דירה 36 טיפוס D1</t>
         </is>
       </c>
       <c r="F9" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G9" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="65">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="I9" s="65">
-        <v>6</v>
-      </c>
-      <c r="N9" s="63">
-        <v>3510000</v>
-      </c>
-      <c r="O9" s="63">
-        <v>3510000</v>
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="L9">
+        <is>
+          <t xml:space="preserve">מזרח </t>
+        </is>
+      </c>
+      <c r="N9" s="65">
+        <v>0</v>
+      </c>
+      <c r="O9" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R9">
         <is>
@@ -689,16 +710,14 @@
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B10">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B10" s="65">
+        <v>15</v>
       </c>
       <c r="C10" s="65">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c t="inlineStr" r="D10">
         <is>
@@ -707,26 +726,31 @@
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">b2 apt 6</t>
+          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
         </is>
       </c>
       <c r="F10" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="65">
-        <v>76</v>
-      </c>
-      <c r="I10" s="65">
-        <v>6</v>
+        <v>89</v>
+      </c>
+      <c t="n" r="I10">
+        <v>10.1</v>
+      </c>
+      <c t="inlineStr" r="L10">
+        <is>
+          <t xml:space="preserve">דרום מזרח </t>
+        </is>
       </c>
       <c r="N10" s="63">
-        <v>4266000</v>
+        <v>5810000</v>
       </c>
       <c r="O10" s="63">
-        <v>4266000</v>
+        <v>5810000</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -737,16 +761,14 @@
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B11">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B11" s="65">
+        <v>15</v>
       </c>
       <c r="C11" s="65">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c t="inlineStr" r="D11">
         <is>
@@ -755,26 +777,31 @@
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">b2 apt 7</t>
+          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
         </is>
       </c>
       <c r="F11" s="65">
+        <v>4</v>
+      </c>
+      <c r="G11" s="65">
         <v>2</v>
       </c>
-      <c r="G11" s="65">
-        <v>3</v>
-      </c>
       <c r="H11" s="65">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c t="n" r="I11">
-        <v>6.5</v>
+        <v>5.9</v>
+      </c>
+      <c t="inlineStr" r="L11">
+        <is>
+          <t xml:space="preserve">דרום </t>
+        </is>
       </c>
       <c r="N11" s="63">
-        <v>4352265</v>
+        <v>4030000</v>
       </c>
       <c r="O11" s="63">
-        <v>4352265</v>
+        <v>4030000</v>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -785,16 +812,14 @@
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B12">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B12" s="65">
+        <v>15</v>
       </c>
       <c r="C12" s="65">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c t="inlineStr" r="D12">
         <is>
@@ -803,26 +828,31 @@
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">b2 apt 8</t>
+          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
         </is>
       </c>
       <c r="F12" s="65">
+        <v>4</v>
+      </c>
+      <c r="G12" s="65">
         <v>2</v>
       </c>
-      <c r="G12" s="65">
-        <v>3</v>
-      </c>
       <c r="H12" s="65">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c t="n" r="I12">
-        <v>6.5</v>
-      </c>
-      <c r="N12" s="63">
-        <v>4852845</v>
-      </c>
-      <c r="O12" s="63">
-        <v>4852845</v>
+        <v>4.2</v>
+      </c>
+      <c t="inlineStr" r="L12">
+        <is>
+          <t xml:space="preserve">דרום </t>
+        </is>
+      </c>
+      <c r="N12" s="65">
+        <v>0</v>
+      </c>
+      <c r="O12" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R12">
         <is>
@@ -833,16 +863,14 @@
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B13">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B13" s="65">
+        <v>15</v>
       </c>
       <c r="C13" s="65">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c t="inlineStr" r="D13">
         <is>
@@ -851,26 +879,31 @@
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">b2 apt 9</t>
+          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
         </is>
       </c>
       <c r="F13" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" s="65">
-        <v>61</v>
-      </c>
-      <c r="I13" s="65">
-        <v>6</v>
+        <v>93</v>
+      </c>
+      <c t="n" r="I13">
+        <v>8.1</v>
+      </c>
+      <c t="inlineStr" r="L13">
+        <is>
+          <t xml:space="preserve">דרום מערב </t>
+        </is>
       </c>
       <c r="N13" s="63">
-        <v>3663360</v>
+        <v>5550000</v>
       </c>
       <c r="O13" s="63">
-        <v>3663360</v>
+        <v>5550000</v>
       </c>
       <c t="inlineStr" r="R13">
         <is>
@@ -881,16 +914,14 @@
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B14">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B14" s="65">
+        <v>15</v>
       </c>
       <c r="C14" s="65">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c t="inlineStr" r="D14">
         <is>
@@ -899,26 +930,31 @@
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">b2 apt 10</t>
+          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
         </is>
       </c>
       <c r="F14" s="65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" s="65">
         <v>4</v>
       </c>
       <c r="H14" s="65">
-        <v>98</v>
-      </c>
-      <c r="I14" s="65">
-        <v>6</v>
+        <v>88</v>
+      </c>
+      <c t="n" r="I14">
+        <v>6.4</v>
+      </c>
+      <c t="inlineStr" r="L14">
+        <is>
+          <t xml:space="preserve">צפון מערב </t>
+        </is>
       </c>
       <c r="N14" s="63">
-        <v>5672160</v>
+        <v>5360000</v>
       </c>
       <c r="O14" s="63">
-        <v>5672160</v>
+        <v>5360000</v>
       </c>
       <c t="inlineStr" r="R14">
         <is>
@@ -929,16 +965,14 @@
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B15">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B15" s="65">
+        <v>15</v>
       </c>
       <c r="C15" s="65">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c t="inlineStr" r="D15">
         <is>
@@ -947,26 +981,31 @@
       </c>
       <c t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">b2 apt 11</t>
+          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
         </is>
       </c>
       <c r="F15" s="65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="65">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c t="n" r="I15">
-        <v>12.5</v>
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L15">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
       </c>
       <c r="N15" s="63">
-        <v>8627850</v>
+        <v>3940000</v>
       </c>
       <c r="O15" s="63">
-        <v>8627850</v>
+        <v>3940000</v>
       </c>
       <c t="inlineStr" r="R15">
         <is>
@@ -977,16 +1016,14 @@
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B16">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B16" s="65">
+        <v>15</v>
       </c>
       <c r="C16" s="65">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c t="inlineStr" r="D16">
         <is>
@@ -995,26 +1032,31 @@
       </c>
       <c t="inlineStr" r="E16">
         <is>
-          <t xml:space="preserve">b2 apt 12</t>
+          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
         </is>
       </c>
       <c r="F16" s="65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="65">
         <v>2</v>
       </c>
       <c r="H16" s="65">
-        <v>62</v>
-      </c>
-      <c r="I16" s="65">
-        <v>6</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I16">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L16">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
       </c>
       <c r="N16" s="63">
-        <v>3720600</v>
+        <v>3940000</v>
       </c>
       <c r="O16" s="63">
-        <v>3720600</v>
+        <v>3940000</v>
       </c>
       <c t="inlineStr" r="R16">
         <is>
@@ -1025,16 +1067,14 @@
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B17">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B17" s="65">
+        <v>15</v>
       </c>
       <c r="C17" s="65">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c t="inlineStr" r="D17">
         <is>
@@ -1043,26 +1083,31 @@
       </c>
       <c t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">b2 apt 13</t>
+          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
         </is>
       </c>
       <c r="F17" s="65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" s="65">
-        <v>98</v>
-      </c>
-      <c r="I17" s="65">
-        <v>6</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I17">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L17">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
       </c>
       <c r="N17" s="63">
-        <v>5781240</v>
+        <v>3940000</v>
       </c>
       <c r="O17" s="63">
-        <v>5781240</v>
+        <v>3940000</v>
       </c>
       <c t="inlineStr" r="R17">
         <is>
@@ -1073,16 +1118,14 @@
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B18">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B18" s="65">
+        <v>15</v>
       </c>
       <c r="C18" s="65">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c t="inlineStr" r="D18">
         <is>
@@ -1091,26 +1134,31 @@
       </c>
       <c t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">b2 apt 14</t>
+          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
         </is>
       </c>
       <c r="F18" s="65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="65">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c t="n" r="I18">
-        <v>11.5</v>
+        <v>6.9</v>
+      </c>
+      <c t="inlineStr" r="L18">
+        <is>
+          <t xml:space="preserve">מזרח </t>
+        </is>
       </c>
       <c r="N18" s="63">
-        <v>8754480</v>
+        <v>5800000</v>
       </c>
       <c r="O18" s="63">
-        <v>8754480</v>
+        <v>5800000</v>
       </c>
       <c t="inlineStr" r="R18">
         <is>
@@ -1121,16 +1169,14 @@
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B19">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B19" s="65">
+        <v>15</v>
       </c>
       <c r="C19" s="65">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c t="inlineStr" r="D19">
         <is>
@@ -1139,7 +1185,7 @@
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">b2 apt 15</t>
+          <t xml:space="preserve">mecher 2023-דירות 46-56-66 טיפוס D2</t>
         </is>
       </c>
       <c r="F19" s="65">
@@ -1149,16 +1195,21 @@
         <v>3</v>
       </c>
       <c r="H19" s="65">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c t="n" r="I19">
-        <v>21.5</v>
+        <v>6.2</v>
+      </c>
+      <c t="inlineStr" r="L19">
+        <is>
+          <t xml:space="preserve">מזרח </t>
+        </is>
       </c>
       <c r="N19" s="63">
-        <v>5788260</v>
+        <v>5200000</v>
       </c>
       <c r="O19" s="63">
-        <v>5788260</v>
+        <v>5200000</v>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1169,16 +1220,14 @@
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B20">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B20" s="65">
+        <v>15</v>
       </c>
       <c r="C20" s="65">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c t="inlineStr" r="D20">
         <is>
@@ -1187,26 +1236,31 @@
       </c>
       <c t="inlineStr" r="E20">
         <is>
-          <t xml:space="preserve">b2 apt 16</t>
+          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
         </is>
       </c>
       <c r="F20" s="65">
         <v>5</v>
       </c>
       <c r="G20" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="65">
-        <v>161</v>
-      </c>
-      <c r="I20" s="65">
-        <v>20</v>
+        <v>89</v>
+      </c>
+      <c t="n" r="I20">
+        <v>10.1</v>
+      </c>
+      <c t="inlineStr" r="L20">
+        <is>
+          <t xml:space="preserve">דרום מזרח </t>
+        </is>
       </c>
       <c r="N20" s="63">
-        <v>10756800</v>
+        <v>5520000</v>
       </c>
       <c r="O20" s="63">
-        <v>10756800</v>
+        <v>5520000</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1217,44 +1271,47 @@
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B21">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B21" s="65">
+        <v>15</v>
       </c>
       <c r="C21" s="65">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c t="inlineStr" r="D21">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c t="inlineStr" r="E21">
         <is>
-          <t xml:space="preserve">b2 pent apt 17 floor1</t>
+          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
         </is>
       </c>
       <c r="F21" s="65">
         <v>5</v>
       </c>
       <c r="G21" s="65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H21" s="65">
-        <v>37</v>
-      </c>
-      <c r="I21" s="65">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c t="n" r="I21">
+        <v>5.9</v>
+      </c>
+      <c t="inlineStr" r="L21">
+        <is>
+          <t xml:space="preserve">דרום </t>
+        </is>
       </c>
       <c r="N21" s="63">
-        <v>2693600</v>
+        <v>3900000</v>
       </c>
       <c r="O21" s="63">
-        <v>2693600</v>
+        <v>3900000</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1265,44 +1322,47 @@
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="B22">
-        <is>
-          <t xml:space="preserve">27-2</t>
-        </is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B22" s="65">
+        <v>15</v>
       </c>
       <c r="C22" s="65">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c t="inlineStr" r="D22">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">b2 pent apt 17 floor2</t>
+          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
         </is>
       </c>
       <c r="F22" s="65">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" s="65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H22" s="65">
-        <v>256</v>
-      </c>
-      <c r="I22" s="65">
-        <v>123</v>
+        <v>54</v>
+      </c>
+      <c t="n" r="I22">
+        <v>4.2</v>
+      </c>
+      <c t="inlineStr" r="L22">
+        <is>
+          <t xml:space="preserve">דרום </t>
+        </is>
       </c>
       <c r="N22" s="63">
-        <v>20129200</v>
+        <v>4210000</v>
       </c>
       <c r="O22" s="63">
-        <v>20129200</v>
+        <v>4210000</v>
       </c>
       <c t="inlineStr" r="R22">
         <is>
@@ -1313,49 +1373,271 @@
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">ניתאי הארבלי</t>
+          <t xml:space="preserve">עדן</t>
         </is>
       </c>
       <c r="B23" s="65">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C23" s="65">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c t="inlineStr" r="D23">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E23">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
         </is>
       </c>
       <c r="F23" s="65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" s="65">
         <v>4</v>
       </c>
       <c r="H23" s="65">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c t="n" r="I23">
-        <v>27.1</v>
+        <v>8.1</v>
       </c>
       <c t="inlineStr" r="L23">
         <is>
+          <t xml:space="preserve">דרום מערב </t>
+        </is>
+      </c>
+      <c r="N23" s="63">
+        <v>5700000</v>
+      </c>
+      <c r="O23" s="63">
+        <v>5700000</v>
+      </c>
+      <c r="P23" s="63">
+        <v>6990000</v>
+      </c>
+      <c t="inlineStr" r="Q23">
+        <is>
+          <t xml:space="preserve">הרשמה: משה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="R23">
+        <is>
+          <t xml:space="preserve">הרשמה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="S23">
+        <is>
+          <t xml:space="preserve">אהרון אברהם</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="T23">
+        <is>
+          <t xml:space="preserve">24/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c t="inlineStr" r="A24">
+        <is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B24" s="65">
+        <v>15</v>
+      </c>
+      <c r="C24" s="65">
+        <v>51</v>
+      </c>
+      <c t="inlineStr" r="D24">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E24">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
+        </is>
+      </c>
+      <c r="F24" s="65">
+        <v>6</v>
+      </c>
+      <c r="G24" s="65">
+        <v>4</v>
+      </c>
+      <c r="H24" s="65">
+        <v>88</v>
+      </c>
+      <c t="n" r="I24">
+        <v>6.4</v>
+      </c>
+      <c t="inlineStr" r="L24">
+        <is>
           <t xml:space="preserve">צפון מערב </t>
         </is>
       </c>
-      <c t="inlineStr" r="M23">
-        <is>
-          <t xml:space="preserve">חזית </t>
-        </is>
-      </c>
-      <c r="N23" s="63">
-        <v>4557874</v>
-      </c>
-      <c r="O23" s="63">
-        <v>4557874</v>
-      </c>
-      <c t="inlineStr" r="R23">
+      <c r="N24" s="63">
+        <v>5510000</v>
+      </c>
+      <c r="O24" s="63">
+        <v>5510000</v>
+      </c>
+      <c t="inlineStr" r="R24">
+        <is>
+          <t xml:space="preserve">פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c t="inlineStr" r="A25">
+        <is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B25" s="65">
+        <v>15</v>
+      </c>
+      <c r="C25" s="65">
+        <v>52</v>
+      </c>
+      <c t="inlineStr" r="D25">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E25">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
+        </is>
+      </c>
+      <c r="F25" s="65">
+        <v>6</v>
+      </c>
+      <c r="G25" s="65">
+        <v>2</v>
+      </c>
+      <c r="H25" s="65">
+        <v>53</v>
+      </c>
+      <c t="n" r="I25">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L25">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
+      </c>
+      <c r="N25" s="63">
+        <v>4100000</v>
+      </c>
+      <c r="O25" s="63">
+        <v>4100000</v>
+      </c>
+      <c t="inlineStr" r="R25">
+        <is>
+          <t xml:space="preserve">פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c t="inlineStr" r="A26">
+        <is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B26" s="65">
+        <v>15</v>
+      </c>
+      <c r="C26" s="65">
+        <v>53</v>
+      </c>
+      <c t="inlineStr" r="D26">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E26">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
+        </is>
+      </c>
+      <c r="F26" s="65">
+        <v>6</v>
+      </c>
+      <c r="G26" s="65">
+        <v>2</v>
+      </c>
+      <c r="H26" s="65">
+        <v>53</v>
+      </c>
+      <c t="n" r="I26">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L26">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
+      </c>
+      <c r="N26" s="63">
+        <v>4110000</v>
+      </c>
+      <c r="O26" s="63">
+        <v>4110000</v>
+      </c>
+      <c t="inlineStr" r="R26">
+        <is>
+          <t xml:space="preserve">פעיל</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c t="inlineStr" r="A27">
+        <is>
+          <t xml:space="preserve">עדן</t>
+        </is>
+      </c>
+      <c r="B27" s="65">
+        <v>15</v>
+      </c>
+      <c r="C27" s="65">
+        <v>54</v>
+      </c>
+      <c t="inlineStr" r="D27">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="E27">
+        <is>
+          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
+        </is>
+      </c>
+      <c r="F27" s="65">
+        <v>6</v>
+      </c>
+      <c r="G27" s="65">
+        <v>2</v>
+      </c>
+      <c r="H27" s="65">
+        <v>53</v>
+      </c>
+      <c t="n" r="I27">
+        <v>6.5</v>
+      </c>
+      <c t="inlineStr" r="L27">
+        <is>
+          <t xml:space="preserve">צפון </t>
+        </is>
+      </c>
+      <c r="N27" s="63">
+        <v>4100000</v>
+      </c>
+      <c r="O27" s="63">
+        <v>4100000</v>
+      </c>
+      <c t="inlineStr" r="R27">
         <is>
           <t xml:space="preserve">פעיל</t>
         </is>

--- a/scraper/downloads/projects_page_5.xlsx
+++ b/scraper/downloads/projects_page_5.xlsx
@@ -201,11 +201,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
-    <col min="1" max="1" width="8.100000000000001" customWidth="1"/>
+    <col min="1" max="1" width="22.950000000000003" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="10.8" customWidth="1"/>
     <col min="4" max="4" width="9.450000000000001" customWidth="1"/>
-    <col min="5" max="5" width="54" customWidth="1"/>
+    <col min="5" max="5" width="28.35" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
     <col min="7" max="7" width="12.15" customWidth="1"/>
     <col min="8" max="8" width="10.8" customWidth="1"/>
@@ -335,14 +335,16 @@
     <row r="3">
       <c t="inlineStr" r="A3">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B3" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B3">
+        <is>
+          <t xml:space="preserve">27-1</t>
+        </is>
       </c>
       <c r="C3" s="65">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="D3">
         <is>
@@ -351,49 +353,64 @@
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t xml:space="preserve">mecher 2023-דירה 29 טיפוס G1</t>
+          <t xml:space="preserve">b1 apt 5</t>
         </is>
       </c>
       <c r="F3" s="65">
         <v>3</v>
       </c>
       <c r="G3" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="65">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I3" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="L3">
-        <is>
-          <t xml:space="preserve">דרום </t>
-        </is>
-      </c>
-      <c r="N3" s="65">
-        <v>0</v>
-      </c>
-      <c r="O3" s="65">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="N3" s="63">
+        <v>4351320</v>
+      </c>
+      <c r="O3" s="63">
+        <v>4351320</v>
+      </c>
+      <c r="P3" s="63">
+        <v>4650000</v>
+      </c>
+      <c t="inlineStr" r="Q3">
+        <is>
+          <t xml:space="preserve">הרשמה: תמימה זיסקינד</t>
+        </is>
       </c>
       <c t="inlineStr" r="R3">
         <is>
-          <t xml:space="preserve">פעיל</t>
+          <t xml:space="preserve">הרשמה</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="S3">
+        <is>
+          <t xml:space="preserve">מנחם אוריאל</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="T3">
+        <is>
+          <t xml:space="preserve">03/09/2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B4" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B4">
+        <is>
+          <t xml:space="preserve">27-1</t>
+        </is>
       </c>
       <c r="C4" s="65">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="D4">
         <is>
@@ -402,31 +419,26 @@
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">mecher 2023-דירה 30 טיפוס H1</t>
+          <t xml:space="preserve">b1 apt 6</t>
         </is>
       </c>
       <c r="F4" s="65">
+        <v>4</v>
+      </c>
+      <c r="G4" s="65">
         <v>3</v>
       </c>
-      <c t="n" r="G4">
-        <v>3.5</v>
-      </c>
       <c r="H4" s="65">
-        <v>94</v>
-      </c>
-      <c t="n" r="I4">
-        <v>3.4</v>
-      </c>
-      <c t="inlineStr" r="L4">
-        <is>
-          <t xml:space="preserve">דרום מערב </t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="I4" s="65">
+        <v>7</v>
       </c>
       <c r="N4" s="63">
-        <v>5340000</v>
+        <v>3863700</v>
       </c>
       <c r="O4" s="63">
-        <v>5340000</v>
+        <v>3863700</v>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -437,47 +449,44 @@
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B5" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B5">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C5" s="65">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="D5">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c t="inlineStr" r="E5">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
+          <t xml:space="preserve">b2 apt 1</t>
         </is>
       </c>
       <c r="F5" s="65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" s="65">
-        <v>88</v>
-      </c>
-      <c t="n" r="I5">
-        <v>6.4</v>
-      </c>
-      <c t="inlineStr" r="L5">
-        <is>
-          <t xml:space="preserve">צפון מערב </t>
-        </is>
+        <v>61</v>
+      </c>
+      <c r="I5" s="65">
+        <v>55</v>
       </c>
       <c r="N5" s="63">
-        <v>5210000</v>
+        <v>4064040</v>
       </c>
       <c r="O5" s="63">
-        <v>5210000</v>
+        <v>4064040</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -488,47 +497,44 @@
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B6" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B6">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C6" s="65">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="D6">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
+          <t xml:space="preserve">b2 apt 2</t>
         </is>
       </c>
       <c r="F6" s="65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I6">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L6">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
+        <v>83</v>
+      </c>
+      <c r="I6" s="65">
+        <v>126</v>
       </c>
       <c r="N6" s="63">
-        <v>3780000</v>
+        <v>5876640</v>
       </c>
       <c r="O6" s="63">
-        <v>3780000</v>
+        <v>5876640</v>
       </c>
       <c t="inlineStr" r="R6">
         <is>
@@ -539,47 +545,44 @@
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B7" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B7">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C7" s="65">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="D7">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
+          <t xml:space="preserve">b2 apt 3</t>
         </is>
       </c>
       <c r="F7" s="65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I7">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L7">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
+        <v>82</v>
+      </c>
+      <c r="I7" s="65">
+        <v>130</v>
       </c>
       <c r="N7" s="63">
-        <v>3770000</v>
+        <v>6237000</v>
       </c>
       <c r="O7" s="63">
-        <v>3770000</v>
+        <v>6237000</v>
       </c>
       <c t="inlineStr" r="R7">
         <is>
@@ -590,83 +593,64 @@
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B8" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B8">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C8" s="65">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="D8">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
+          <t xml:space="preserve">b2 apt 4</t>
         </is>
       </c>
       <c r="F8" s="65">
+        <v>1</v>
+      </c>
+      <c r="G8" s="65">
         <v>4</v>
       </c>
-      <c r="G8" s="65">
-        <v>3</v>
-      </c>
       <c r="H8" s="65">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c t="n" r="I8">
-        <v>6.9</v>
-      </c>
-      <c t="inlineStr" r="L8">
-        <is>
-          <t xml:space="preserve">מזרח </t>
-        </is>
+        <v>75.5</v>
       </c>
       <c r="N8" s="63">
-        <v>5650000</v>
+        <v>5167800</v>
       </c>
       <c r="O8" s="63">
-        <v>5650000</v>
-      </c>
-      <c r="P8" s="63">
-        <v>6750000</v>
-      </c>
-      <c t="inlineStr" r="Q8">
-        <is>
-          <t xml:space="preserve">הרשמה: Daniel Bassan</t>
-        </is>
+        <v>5167800</v>
       </c>
       <c t="inlineStr" r="R8">
         <is>
-          <t xml:space="preserve">הרשמה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="S8">
-        <is>
-          <t xml:space="preserve">יניב אשכנזי</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="T8">
-        <is>
-          <t xml:space="preserve">30/03/2025</t>
+          <t xml:space="preserve">פעיל</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B9" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B9">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C9" s="65">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="D9">
         <is>
@@ -675,31 +659,26 @@
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">mecher 2023-דירה 36 טיפוס D1</t>
+          <t xml:space="preserve">b2 apt 5</t>
         </is>
       </c>
       <c r="F9" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="65">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="I9" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="L9">
-        <is>
-          <t xml:space="preserve">מזרח </t>
-        </is>
-      </c>
-      <c r="N9" s="65">
-        <v>0</v>
-      </c>
-      <c r="O9" s="65">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="N9" s="63">
+        <v>3510000</v>
+      </c>
+      <c r="O9" s="63">
+        <v>3510000</v>
       </c>
       <c t="inlineStr" r="R9">
         <is>
@@ -710,14 +689,16 @@
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B10" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B10">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C10" s="65">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="D10">
         <is>
@@ -726,31 +707,26 @@
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
+          <t xml:space="preserve">b2 apt 6</t>
         </is>
       </c>
       <c r="F10" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="65">
-        <v>89</v>
-      </c>
-      <c t="n" r="I10">
-        <v>10.1</v>
-      </c>
-      <c t="inlineStr" r="L10">
-        <is>
-          <t xml:space="preserve">דרום מזרח </t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="I10" s="65">
+        <v>6</v>
       </c>
       <c r="N10" s="63">
-        <v>5810000</v>
+        <v>4266000</v>
       </c>
       <c r="O10" s="63">
-        <v>5810000</v>
+        <v>4266000</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -761,14 +737,16 @@
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B11" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B11">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C11" s="65">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c t="inlineStr" r="D11">
         <is>
@@ -777,31 +755,26 @@
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
+          <t xml:space="preserve">b2 apt 7</t>
         </is>
       </c>
       <c r="F11" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="65">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c t="n" r="I11">
-        <v>5.9</v>
-      </c>
-      <c t="inlineStr" r="L11">
-        <is>
-          <t xml:space="preserve">דרום </t>
-        </is>
+        <v>6.5</v>
       </c>
       <c r="N11" s="63">
-        <v>4030000</v>
+        <v>4352265</v>
       </c>
       <c r="O11" s="63">
-        <v>4030000</v>
+        <v>4352265</v>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -812,14 +785,16 @@
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B12" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B12">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C12" s="65">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c t="inlineStr" r="D12">
         <is>
@@ -828,31 +803,26 @@
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
+          <t xml:space="preserve">b2 apt 8</t>
         </is>
       </c>
       <c r="F12" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="65">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c t="n" r="I12">
-        <v>4.2</v>
-      </c>
-      <c t="inlineStr" r="L12">
-        <is>
-          <t xml:space="preserve">דרום </t>
-        </is>
-      </c>
-      <c r="N12" s="65">
-        <v>0</v>
-      </c>
-      <c r="O12" s="65">
-        <v>0</v>
+        <v>6.5</v>
+      </c>
+      <c r="N12" s="63">
+        <v>4852845</v>
+      </c>
+      <c r="O12" s="63">
+        <v>4852845</v>
       </c>
       <c t="inlineStr" r="R12">
         <is>
@@ -863,14 +833,16 @@
     <row r="13">
       <c t="inlineStr" r="A13">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B13" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B13">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C13" s="65">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c t="inlineStr" r="D13">
         <is>
@@ -879,31 +851,26 @@
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
+          <t xml:space="preserve">b2 apt 9</t>
         </is>
       </c>
       <c r="F13" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" s="65">
-        <v>93</v>
-      </c>
-      <c t="n" r="I13">
-        <v>8.1</v>
-      </c>
-      <c t="inlineStr" r="L13">
-        <is>
-          <t xml:space="preserve">דרום מערב </t>
-        </is>
+        <v>61</v>
+      </c>
+      <c r="I13" s="65">
+        <v>6</v>
       </c>
       <c r="N13" s="63">
-        <v>5550000</v>
+        <v>3663360</v>
       </c>
       <c r="O13" s="63">
-        <v>5550000</v>
+        <v>3663360</v>
       </c>
       <c t="inlineStr" r="R13">
         <is>
@@ -914,14 +881,16 @@
     <row r="14">
       <c t="inlineStr" r="A14">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B14" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B14">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C14" s="65">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c t="inlineStr" r="D14">
         <is>
@@ -930,31 +899,26 @@
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
+          <t xml:space="preserve">b2 apt 10</t>
         </is>
       </c>
       <c r="F14" s="65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14" s="65">
         <v>4</v>
       </c>
       <c r="H14" s="65">
-        <v>88</v>
-      </c>
-      <c t="n" r="I14">
-        <v>6.4</v>
-      </c>
-      <c t="inlineStr" r="L14">
-        <is>
-          <t xml:space="preserve">צפון מערב </t>
-        </is>
+        <v>98</v>
+      </c>
+      <c r="I14" s="65">
+        <v>6</v>
       </c>
       <c r="N14" s="63">
-        <v>5360000</v>
+        <v>5672160</v>
       </c>
       <c r="O14" s="63">
-        <v>5360000</v>
+        <v>5672160</v>
       </c>
       <c t="inlineStr" r="R14">
         <is>
@@ -965,14 +929,16 @@
     <row r="15">
       <c t="inlineStr" r="A15">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B15" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B15">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C15" s="65">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c t="inlineStr" r="D15">
         <is>
@@ -981,31 +947,26 @@
       </c>
       <c t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
+          <t xml:space="preserve">b2 apt 11</t>
         </is>
       </c>
       <c r="F15" s="65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="65">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c t="n" r="I15">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L15">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
+        <v>12.5</v>
       </c>
       <c r="N15" s="63">
-        <v>3940000</v>
+        <v>8627850</v>
       </c>
       <c r="O15" s="63">
-        <v>3940000</v>
+        <v>8627850</v>
       </c>
       <c t="inlineStr" r="R15">
         <is>
@@ -1016,14 +977,16 @@
     <row r="16">
       <c t="inlineStr" r="A16">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B16" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C16" s="65">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c t="inlineStr" r="D16">
         <is>
@@ -1032,31 +995,26 @@
       </c>
       <c t="inlineStr" r="E16">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
+          <t xml:space="preserve">b2 apt 12</t>
         </is>
       </c>
       <c r="F16" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="65">
         <v>2</v>
       </c>
       <c r="H16" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I16">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L16">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="I16" s="65">
+        <v>6</v>
       </c>
       <c r="N16" s="63">
-        <v>3940000</v>
+        <v>3720600</v>
       </c>
       <c r="O16" s="63">
-        <v>3940000</v>
+        <v>3720600</v>
       </c>
       <c t="inlineStr" r="R16">
         <is>
@@ -1067,14 +1025,16 @@
     <row r="17">
       <c t="inlineStr" r="A17">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B17" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B17">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C17" s="65">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c t="inlineStr" r="D17">
         <is>
@@ -1083,31 +1043,26 @@
       </c>
       <c t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
+          <t xml:space="preserve">b2 apt 13</t>
         </is>
       </c>
       <c r="F17" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I17">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L17">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
+        <v>98</v>
+      </c>
+      <c r="I17" s="65">
+        <v>6</v>
       </c>
       <c r="N17" s="63">
-        <v>3940000</v>
+        <v>5781240</v>
       </c>
       <c r="O17" s="63">
-        <v>3940000</v>
+        <v>5781240</v>
       </c>
       <c t="inlineStr" r="R17">
         <is>
@@ -1118,14 +1073,16 @@
     <row r="18">
       <c t="inlineStr" r="A18">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B18" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B18">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C18" s="65">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c t="inlineStr" r="D18">
         <is>
@@ -1134,31 +1091,26 @@
       </c>
       <c t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 5-15-25-35-45-55-65 טיפוס C</t>
+          <t xml:space="preserve">b2 apt 14</t>
         </is>
       </c>
       <c r="F18" s="65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="65">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c t="n" r="I18">
-        <v>6.9</v>
-      </c>
-      <c t="inlineStr" r="L18">
-        <is>
-          <t xml:space="preserve">מזרח </t>
-        </is>
+        <v>11.5</v>
       </c>
       <c r="N18" s="63">
-        <v>5800000</v>
+        <v>8754480</v>
       </c>
       <c r="O18" s="63">
-        <v>5800000</v>
+        <v>8754480</v>
       </c>
       <c t="inlineStr" r="R18">
         <is>
@@ -1169,15 +1121,17 @@
     <row r="19">
       <c t="inlineStr" r="A19">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B19" s="65">
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B19">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
+      </c>
+      <c r="C19" s="65">
         <v>15</v>
       </c>
-      <c r="C19" s="65">
-        <v>46</v>
-      </c>
       <c t="inlineStr" r="D19">
         <is>
           <t xml:space="preserve">דירה</t>
@@ -1185,7 +1139,7 @@
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 46-56-66 טיפוס D2</t>
+          <t xml:space="preserve">b2 apt 15</t>
         </is>
       </c>
       <c r="F19" s="65">
@@ -1195,21 +1149,16 @@
         <v>3</v>
       </c>
       <c r="H19" s="65">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c t="n" r="I19">
-        <v>6.2</v>
-      </c>
-      <c t="inlineStr" r="L19">
-        <is>
-          <t xml:space="preserve">מזרח </t>
-        </is>
+        <v>21.5</v>
       </c>
       <c r="N19" s="63">
-        <v>5200000</v>
+        <v>5788260</v>
       </c>
       <c r="O19" s="63">
-        <v>5200000</v>
+        <v>5788260</v>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1220,14 +1169,16 @@
     <row r="20">
       <c t="inlineStr" r="A20">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B20" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C20" s="65">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c t="inlineStr" r="D20">
         <is>
@@ -1236,31 +1187,26 @@
       </c>
       <c t="inlineStr" r="E20">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 37-47-57-67 טיפוס E2</t>
+          <t xml:space="preserve">b2 apt 16</t>
         </is>
       </c>
       <c r="F20" s="65">
         <v>5</v>
       </c>
       <c r="G20" s="65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="65">
-        <v>89</v>
-      </c>
-      <c t="n" r="I20">
-        <v>10.1</v>
-      </c>
-      <c t="inlineStr" r="L20">
-        <is>
-          <t xml:space="preserve">דרום מזרח </t>
-        </is>
+        <v>161</v>
+      </c>
+      <c r="I20" s="65">
+        <v>20</v>
       </c>
       <c r="N20" s="63">
-        <v>5520000</v>
+        <v>10756800</v>
       </c>
       <c r="O20" s="63">
-        <v>5520000</v>
+        <v>10756800</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1271,47 +1217,44 @@
     <row r="21">
       <c t="inlineStr" r="A21">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B21" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C21" s="65">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c t="inlineStr" r="D21">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c t="inlineStr" r="E21">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 38-48-58-68 טיפוס F3</t>
+          <t xml:space="preserve">b2 pent apt 17 floor1</t>
         </is>
       </c>
       <c r="F21" s="65">
         <v>5</v>
       </c>
       <c r="G21" s="65">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H21" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I21">
-        <v>5.9</v>
-      </c>
-      <c t="inlineStr" r="L21">
-        <is>
-          <t xml:space="preserve">דרום </t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="I21" s="65">
+        <v>0</v>
       </c>
       <c r="N21" s="63">
-        <v>3900000</v>
+        <v>2693600</v>
       </c>
       <c r="O21" s="63">
-        <v>3900000</v>
+        <v>2693600</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1322,47 +1265,44 @@
     <row r="22">
       <c t="inlineStr" r="A22">
         <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B22" s="65">
-        <v>15</v>
+          <t xml:space="preserve">שמואל הנגיד-רזדנס</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">27-2</t>
+        </is>
       </c>
       <c r="C22" s="65">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c t="inlineStr" r="D22">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">mecher 2023-דירות 39-49-59-69 טיפוס G2</t>
+          <t xml:space="preserve">b2 pent apt 17 floor2</t>
         </is>
       </c>
       <c r="F22" s="65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" s="65">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H22" s="65">
-        <v>54</v>
-      </c>
-      <c t="n" r="I22">
-        <v>4.2</v>
-      </c>
-      <c t="inlineStr" r="L22">
-        <is>
-          <t xml:space="preserve">דרום </t>
-        </is>
+        <v>256</v>
+      </c>
+      <c r="I22" s="65">
+        <v>123</v>
       </c>
       <c r="N22" s="63">
-        <v>4210000</v>
+        <v>20129200</v>
       </c>
       <c r="O22" s="63">
-        <v>4210000</v>
+        <v>20129200</v>
       </c>
       <c t="inlineStr" r="R22">
         <is>
@@ -1373,271 +1313,49 @@
     <row r="23">
       <c t="inlineStr" r="A23">
         <is>
-          <t xml:space="preserve">עדן</t>
+          <t xml:space="preserve">ניתאי הארבלי</t>
         </is>
       </c>
       <c r="B23" s="65">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C23" s="65">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="D23">
         <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E23">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 40,50,60,70 טיפוס H2</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c r="F23" s="65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G23" s="65">
         <v>4</v>
       </c>
       <c r="H23" s="65">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c t="n" r="I23">
-        <v>8.1</v>
+        <v>27.1</v>
       </c>
       <c t="inlineStr" r="L23">
         <is>
-          <t xml:space="preserve">דרום מערב </t>
+          <t xml:space="preserve">צפון מערב </t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M23">
+        <is>
+          <t xml:space="preserve">חזית </t>
         </is>
       </c>
       <c r="N23" s="63">
-        <v>5700000</v>
+        <v>4557874</v>
       </c>
       <c r="O23" s="63">
-        <v>5700000</v>
-      </c>
-      <c r="P23" s="63">
-        <v>6990000</v>
-      </c>
-      <c t="inlineStr" r="Q23">
-        <is>
-          <t xml:space="preserve">הרשמה: משה</t>
-        </is>
+        <v>4557874</v>
       </c>
       <c t="inlineStr" r="R23">
-        <is>
-          <t xml:space="preserve">הרשמה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="S23">
-        <is>
-          <t xml:space="preserve">אהרון אברהם</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="T23">
-        <is>
-          <t xml:space="preserve">24/05/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c t="inlineStr" r="A24">
-        <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B24" s="65">
-        <v>15</v>
-      </c>
-      <c r="C24" s="65">
-        <v>51</v>
-      </c>
-      <c t="inlineStr" r="D24">
-        <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E24">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 1-11-21-31-41-51-61 טיפוס A</t>
-        </is>
-      </c>
-      <c r="F24" s="65">
-        <v>6</v>
-      </c>
-      <c r="G24" s="65">
-        <v>4</v>
-      </c>
-      <c r="H24" s="65">
-        <v>88</v>
-      </c>
-      <c t="n" r="I24">
-        <v>6.4</v>
-      </c>
-      <c t="inlineStr" r="L24">
-        <is>
-          <t xml:space="preserve">צפון מערב </t>
-        </is>
-      </c>
-      <c r="N24" s="63">
-        <v>5510000</v>
-      </c>
-      <c r="O24" s="63">
-        <v>5510000</v>
-      </c>
-      <c t="inlineStr" r="R24">
-        <is>
-          <t xml:space="preserve">פעיל</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c t="inlineStr" r="A25">
-        <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B25" s="65">
-        <v>15</v>
-      </c>
-      <c r="C25" s="65">
-        <v>52</v>
-      </c>
-      <c t="inlineStr" r="D25">
-        <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E25">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 2-12-22-32-42-52-62 טיפוס B</t>
-        </is>
-      </c>
-      <c r="F25" s="65">
-        <v>6</v>
-      </c>
-      <c r="G25" s="65">
-        <v>2</v>
-      </c>
-      <c r="H25" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I25">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L25">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
-      </c>
-      <c r="N25" s="63">
-        <v>4100000</v>
-      </c>
-      <c r="O25" s="63">
-        <v>4100000</v>
-      </c>
-      <c t="inlineStr" r="R25">
-        <is>
-          <t xml:space="preserve">פעיל</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c t="inlineStr" r="A26">
-        <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B26" s="65">
-        <v>15</v>
-      </c>
-      <c r="C26" s="65">
-        <v>53</v>
-      </c>
-      <c t="inlineStr" r="D26">
-        <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E26">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 3-13-23-33-43-53-63 טיפוס B1</t>
-        </is>
-      </c>
-      <c r="F26" s="65">
-        <v>6</v>
-      </c>
-      <c r="G26" s="65">
-        <v>2</v>
-      </c>
-      <c r="H26" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I26">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L26">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
-      </c>
-      <c r="N26" s="63">
-        <v>4110000</v>
-      </c>
-      <c r="O26" s="63">
-        <v>4110000</v>
-      </c>
-      <c t="inlineStr" r="R26">
-        <is>
-          <t xml:space="preserve">פעיל</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c t="inlineStr" r="A27">
-        <is>
-          <t xml:space="preserve">עדן</t>
-        </is>
-      </c>
-      <c r="B27" s="65">
-        <v>15</v>
-      </c>
-      <c r="C27" s="65">
-        <v>54</v>
-      </c>
-      <c t="inlineStr" r="D27">
-        <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="E27">
-        <is>
-          <t xml:space="preserve">mecher 2023-דירות 4-14-24-34-44-54-64 טיפוס B2</t>
-        </is>
-      </c>
-      <c r="F27" s="65">
-        <v>6</v>
-      </c>
-      <c r="G27" s="65">
-        <v>2</v>
-      </c>
-      <c r="H27" s="65">
-        <v>53</v>
-      </c>
-      <c t="n" r="I27">
-        <v>6.5</v>
-      </c>
-      <c t="inlineStr" r="L27">
-        <is>
-          <t xml:space="preserve">צפון </t>
-        </is>
-      </c>
-      <c r="N27" s="63">
-        <v>4100000</v>
-      </c>
-      <c r="O27" s="63">
-        <v>4100000</v>
-      </c>
-      <c t="inlineStr" r="R27">
         <is>
           <t xml:space="preserve">פעיל</t>
         </is>
